--- a/Team-Data/2014-15/2-17-2014-15.xlsx
+++ b/Team-Data/2014-15/2-17-2014-15.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>6.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE2" t="n">
         <v>1</v>
@@ -772,7 +839,7 @@
         <v>1</v>
       </c>
       <c r="AO2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AP2" t="n">
         <v>17</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>2-17-2014-15</t>
+          <t>2015-02-17</t>
         </is>
       </c>
     </row>
@@ -969,7 +1036,7 @@
         <v>11</v>
       </c>
       <c r="AT3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AU3" t="n">
         <v>4</v>
@@ -984,10 +1051,10 @@
         <v>28</v>
       </c>
       <c r="AY3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA3" t="n">
         <v>30</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>2-17-2014-15</t>
+          <t>2015-02-17</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>-4</v>
       </c>
       <c r="AD4" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AE4" t="n">
         <v>19</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>2-17-2014-15</t>
+          <t>2015-02-17</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-2.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AE5" t="n">
         <v>17</v>
@@ -1348,7 +1415,7 @@
         <v>7</v>
       </c>
       <c r="AY5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ5" t="n">
         <v>4</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>2-17-2014-15</t>
+          <t>2015-02-17</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1534,7 @@
         <v>3.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE6" t="n">
         <v>9</v>
@@ -1509,7 +1576,7 @@
         <v>3</v>
       </c>
       <c r="AR6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AS6" t="n">
         <v>8</v>
@@ -1530,19 +1597,19 @@
         <v>1</v>
       </c>
       <c r="AY6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ6" t="n">
         <v>2</v>
       </c>
       <c r="BA6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB6" t="n">
         <v>9</v>
       </c>
       <c r="BC6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>2-17-2014-15</t>
+          <t>2015-02-17</t>
         </is>
       </c>
     </row>
@@ -1649,10 +1716,10 @@
         <v>2.9</v>
       </c>
       <c r="AD7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AF7" t="n">
         <v>12</v>
@@ -1670,7 +1737,7 @@
         <v>21</v>
       </c>
       <c r="AK7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AL7" t="n">
         <v>8</v>
@@ -1685,7 +1752,7 @@
         <v>8</v>
       </c>
       <c r="AP7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ7" t="n">
         <v>18</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>2-17-2014-15</t>
+          <t>2015-02-17</t>
         </is>
       </c>
     </row>
@@ -1753,25 +1820,25 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E8" t="n">
         <v>36</v>
       </c>
       <c r="F8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G8" t="n">
-        <v>0.667</v>
+        <v>0.655</v>
       </c>
       <c r="H8" t="n">
-        <v>48.6</v>
+        <v>48.5</v>
       </c>
       <c r="I8" t="n">
         <v>40</v>
       </c>
       <c r="J8" t="n">
-        <v>86.09999999999999</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="K8" t="n">
         <v>0.465</v>
@@ -1780,34 +1847,34 @@
         <v>9.699999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>27.1</v>
+        <v>27</v>
       </c>
       <c r="N8" t="n">
-        <v>0.357</v>
+        <v>0.358</v>
       </c>
       <c r="O8" t="n">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
       <c r="P8" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.756</v>
+        <v>0.757</v>
       </c>
       <c r="R8" t="n">
         <v>10.8</v>
       </c>
       <c r="S8" t="n">
-        <v>31.7</v>
+        <v>31.6</v>
       </c>
       <c r="T8" t="n">
-        <v>42.5</v>
+        <v>42.3</v>
       </c>
       <c r="U8" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="V8" t="n">
-        <v>12.4</v>
+        <v>12.3</v>
       </c>
       <c r="W8" t="n">
         <v>8.1</v>
@@ -1825,13 +1892,13 @@
         <v>21.9</v>
       </c>
       <c r="AB8" t="n">
-        <v>106.5</v>
+        <v>106.3</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE8" t="n">
         <v>4</v>
@@ -1843,7 +1910,7 @@
         <v>7</v>
       </c>
       <c r="AH8" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AI8" t="n">
         <v>2</v>
@@ -1855,13 +1922,13 @@
         <v>6</v>
       </c>
       <c r="AL8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AM8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AO8" t="n">
         <v>17</v>
@@ -1876,10 +1943,10 @@
         <v>16</v>
       </c>
       <c r="AS8" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AT8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AU8" t="n">
         <v>8</v>
@@ -1900,7 +1967,7 @@
         <v>14</v>
       </c>
       <c r="BA8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB8" t="n">
         <v>3</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>2-17-2014-15</t>
+          <t>2015-02-17</t>
         </is>
       </c>
     </row>
@@ -2025,13 +2092,13 @@
         <v>23</v>
       </c>
       <c r="AH9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI9" t="n">
         <v>16</v>
       </c>
       <c r="AJ9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AK9" t="n">
         <v>26</v>
@@ -2055,7 +2122,7 @@
         <v>23</v>
       </c>
       <c r="AR9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AS9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>2-17-2014-15</t>
+          <t>2015-02-17</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-1.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE10" t="n">
         <v>19</v>
@@ -2252,7 +2319,7 @@
         <v>8</v>
       </c>
       <c r="AW10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AX10" t="n">
         <v>17</v>
@@ -2264,7 +2331,7 @@
         <v>7</v>
       </c>
       <c r="BA10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BB10" t="n">
         <v>21</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>2-17-2014-15</t>
+          <t>2015-02-17</t>
         </is>
       </c>
     </row>
@@ -2404,13 +2471,13 @@
         <v>2</v>
       </c>
       <c r="AM11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AN11" t="n">
         <v>2</v>
       </c>
       <c r="AO11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AP11" t="n">
         <v>23</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>2-17-2014-15</t>
+          <t>2015-02-17</t>
         </is>
       </c>
     </row>
@@ -2481,46 +2548,46 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F12" t="n">
         <v>17</v>
       </c>
       <c r="G12" t="n">
-        <v>0.673</v>
+        <v>0.679</v>
       </c>
       <c r="H12" t="n">
         <v>48.4</v>
       </c>
       <c r="I12" t="n">
-        <v>36.9</v>
+        <v>36.8</v>
       </c>
       <c r="J12" t="n">
-        <v>84</v>
+        <v>83.8</v>
       </c>
       <c r="K12" t="n">
-        <v>0.44</v>
+        <v>0.439</v>
       </c>
       <c r="L12" t="n">
         <v>11.8</v>
       </c>
       <c r="M12" t="n">
-        <v>33.7</v>
+        <v>33.6</v>
       </c>
       <c r="N12" t="n">
-        <v>0.349</v>
+        <v>0.351</v>
       </c>
       <c r="O12" t="n">
-        <v>17.4</v>
+        <v>17.7</v>
       </c>
       <c r="P12" t="n">
-        <v>24.2</v>
+        <v>24.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.72</v>
+        <v>0.718</v>
       </c>
       <c r="R12" t="n">
         <v>12.1</v>
@@ -2529,7 +2596,7 @@
         <v>31.3</v>
       </c>
       <c r="T12" t="n">
-        <v>43.3</v>
+        <v>43.4</v>
       </c>
       <c r="U12" t="n">
         <v>21.7</v>
@@ -2538,37 +2605,37 @@
         <v>16.9</v>
       </c>
       <c r="W12" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="X12" t="n">
         <v>4.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>22.5</v>
+        <v>22.7</v>
       </c>
       <c r="AA12" t="n">
-        <v>20.3</v>
+        <v>20.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>103</v>
+        <v>103.1</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="AD12" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="AE12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AF12" t="n">
         <v>4</v>
       </c>
       <c r="AG12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AH12" t="n">
         <v>15</v>
@@ -2577,7 +2644,7 @@
         <v>20</v>
       </c>
       <c r="AJ12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AK12" t="n">
         <v>22</v>
@@ -2589,19 +2656,19 @@
         <v>1</v>
       </c>
       <c r="AN12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AP12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AQ12" t="n">
         <v>28</v>
       </c>
       <c r="AR12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AS12" t="n">
         <v>23</v>
@@ -2619,7 +2686,7 @@
         <v>2</v>
       </c>
       <c r="AX12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AY12" t="n">
         <v>26</v>
@@ -2628,13 +2695,13 @@
         <v>29</v>
       </c>
       <c r="BA12" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BB12" t="n">
         <v>7</v>
       </c>
       <c r="BC12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>2-17-2014-15</t>
+          <t>2015-02-17</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>-1.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE13" t="n">
         <v>19</v>
@@ -2759,13 +2826,13 @@
         <v>24</v>
       </c>
       <c r="AJ13" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK13" t="n">
         <v>25</v>
       </c>
       <c r="AL13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AM13" t="n">
         <v>18</v>
@@ -2780,7 +2847,7 @@
         <v>25</v>
       </c>
       <c r="AQ13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AR13" t="n">
         <v>19</v>
@@ -2804,7 +2871,7 @@
         <v>22</v>
       </c>
       <c r="AY13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ13" t="n">
         <v>16</v>
@@ -2813,7 +2880,7 @@
         <v>10</v>
       </c>
       <c r="BB13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BC13" t="n">
         <v>17</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>2-17-2014-15</t>
+          <t>2015-02-17</t>
         </is>
       </c>
     </row>
@@ -2923,13 +2990,13 @@
         <v>6</v>
       </c>
       <c r="AD14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF14" t="n">
         <v>7</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>8</v>
       </c>
       <c r="AG14" t="n">
         <v>8</v>
@@ -2947,7 +3014,7 @@
         <v>2</v>
       </c>
       <c r="AL14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AM14" t="n">
         <v>6</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>2-17-2014-15</t>
+          <t>2015-02-17</t>
         </is>
       </c>
     </row>
@@ -3027,58 +3094,58 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E15" t="n">
         <v>13</v>
       </c>
       <c r="F15" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G15" t="n">
-        <v>0.25</v>
+        <v>0.245</v>
       </c>
       <c r="H15" t="n">
         <v>48.7</v>
       </c>
       <c r="I15" t="n">
-        <v>37.3</v>
+        <v>37.2</v>
       </c>
       <c r="J15" t="n">
-        <v>86.3</v>
+        <v>86.2</v>
       </c>
       <c r="K15" t="n">
-        <v>0.433</v>
+        <v>0.431</v>
       </c>
       <c r="L15" t="n">
         <v>6.8</v>
       </c>
       <c r="M15" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="N15" t="n">
         <v>0.349</v>
       </c>
       <c r="O15" t="n">
-        <v>17.8</v>
+        <v>18</v>
       </c>
       <c r="P15" t="n">
-        <v>23.8</v>
+        <v>24.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.745</v>
+        <v>0.746</v>
       </c>
       <c r="R15" t="n">
         <v>11.9</v>
       </c>
       <c r="S15" t="n">
-        <v>31.9</v>
+        <v>31.7</v>
       </c>
       <c r="T15" t="n">
-        <v>43.8</v>
+        <v>43.6</v>
       </c>
       <c r="U15" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="V15" t="n">
         <v>13.1</v>
@@ -3093,19 +3160,19 @@
         <v>4.6</v>
       </c>
       <c r="Z15" t="n">
-        <v>20.9</v>
+        <v>21.2</v>
       </c>
       <c r="AA15" t="n">
-        <v>19.7</v>
+        <v>19.9</v>
       </c>
       <c r="AB15" t="n">
-        <v>99.3</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6.9</v>
+        <v>-7.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="AE15" t="n">
         <v>27</v>
@@ -3117,13 +3184,13 @@
         <v>27</v>
       </c>
       <c r="AH15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AJ15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AK15" t="n">
         <v>27</v>
@@ -3138,10 +3205,10 @@
         <v>17</v>
       </c>
       <c r="AO15" t="n">
+        <v>9</v>
+      </c>
+      <c r="AP15" t="n">
         <v>10</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>12</v>
       </c>
       <c r="AQ15" t="n">
         <v>19</v>
@@ -3150,13 +3217,13 @@
         <v>8</v>
       </c>
       <c r="AS15" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AT15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AV15" t="n">
         <v>6</v>
@@ -3171,13 +3238,13 @@
         <v>12</v>
       </c>
       <c r="AZ15" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BA15" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BB15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BC15" t="n">
         <v>27</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>2-17-2014-15</t>
+          <t>2015-02-17</t>
         </is>
       </c>
     </row>
@@ -3299,7 +3366,7 @@
         <v>3</v>
       </c>
       <c r="AH16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI16" t="n">
         <v>7</v>
@@ -3323,7 +3390,7 @@
         <v>6</v>
       </c>
       <c r="AP16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ16" t="n">
         <v>5</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>2-17-2014-15</t>
+          <t>2015-02-17</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>-3.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AE17" t="n">
         <v>17</v>
@@ -3538,7 +3605,7 @@
         <v>12</v>
       </c>
       <c r="BA17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB17" t="n">
         <v>28</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>2-17-2014-15</t>
+          <t>2015-02-17</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3733,7 @@
         <v>8</v>
       </c>
       <c r="AI18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AJ18" t="n">
         <v>24</v>
@@ -3720,10 +3787,10 @@
         <v>27</v>
       </c>
       <c r="BA18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB18" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BC18" t="n">
         <v>13</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>2-17-2014-15</t>
+          <t>2015-02-17</t>
         </is>
       </c>
     </row>
@@ -3845,10 +3912,10 @@
         <v>29</v>
       </c>
       <c r="AH19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AJ19" t="n">
         <v>11</v>
@@ -3875,7 +3942,7 @@
         <v>14</v>
       </c>
       <c r="AR19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS19" t="n">
         <v>30</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>2-17-2014-15</t>
+          <t>2015-02-17</t>
         </is>
       </c>
     </row>
@@ -3937,16 +4004,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E20" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F20" t="n">
         <v>26</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5</v>
+        <v>0.509</v>
       </c>
       <c r="H20" t="n">
         <v>48.2</v>
@@ -3955,10 +4022,10 @@
         <v>38</v>
       </c>
       <c r="J20" t="n">
-        <v>83.59999999999999</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>0.454</v>
+        <v>0.453</v>
       </c>
       <c r="L20" t="n">
         <v>6.8</v>
@@ -3967,25 +4034,25 @@
         <v>19.1</v>
       </c>
       <c r="N20" t="n">
-        <v>0.356</v>
+        <v>0.354</v>
       </c>
       <c r="O20" t="n">
         <v>17.1</v>
       </c>
       <c r="P20" t="n">
-        <v>22.2</v>
+        <v>22.4</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.769</v>
+        <v>0.762</v>
       </c>
       <c r="R20" t="n">
-        <v>12</v>
+        <v>12.2</v>
       </c>
       <c r="S20" t="n">
-        <v>31.7</v>
+        <v>31.8</v>
       </c>
       <c r="T20" t="n">
-        <v>43.7</v>
+        <v>44</v>
       </c>
       <c r="U20" t="n">
         <v>21.4</v>
@@ -3994,28 +4061,28 @@
         <v>13.1</v>
       </c>
       <c r="W20" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="X20" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="Y20" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="Z20" t="n">
         <v>18.8</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="AB20" t="n">
         <v>99.8</v>
       </c>
       <c r="AC20" t="n">
-        <v>-0.2</v>
+        <v>0.1</v>
       </c>
       <c r="AD20" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="AE20" t="n">
         <v>16</v>
@@ -4030,16 +4097,16 @@
         <v>22</v>
       </c>
       <c r="AI20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AJ20" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK20" t="n">
         <v>14</v>
       </c>
-      <c r="AK20" t="n">
-        <v>13</v>
-      </c>
       <c r="AL20" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AM20" t="n">
         <v>24</v>
@@ -4054,28 +4121,28 @@
         <v>18</v>
       </c>
       <c r="AQ20" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>19</v>
+      </c>
+      <c r="AT20" t="n">
         <v>10</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>6</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>20</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>14</v>
       </c>
       <c r="AU20" t="n">
         <v>17</v>
       </c>
       <c r="AV20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW20" t="n">
         <v>26</v>
       </c>
       <c r="AX20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AY20" t="n">
         <v>30</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>2-17-2014-15</t>
+          <t>2015-02-17</t>
         </is>
       </c>
     </row>
@@ -4236,7 +4303,7 @@
         <v>30</v>
       </c>
       <c r="AQ21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR21" t="n">
         <v>17</v>
@@ -4254,7 +4321,7 @@
         <v>16</v>
       </c>
       <c r="AW21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX21" t="n">
         <v>26</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>2-17-2014-15</t>
+          <t>2015-02-17</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4458,7 @@
         <v>15</v>
       </c>
       <c r="AH22" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI22" t="n">
         <v>14</v>
@@ -4412,10 +4479,10 @@
         <v>25</v>
       </c>
       <c r="AO22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AP22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ22" t="n">
         <v>17</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>2-17-2014-15</t>
+          <t>2015-02-17</t>
         </is>
       </c>
     </row>
@@ -4483,34 +4550,34 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E23" t="n">
         <v>17</v>
       </c>
       <c r="F23" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G23" t="n">
-        <v>0.309</v>
+        <v>0.304</v>
       </c>
       <c r="H23" t="n">
         <v>48.2</v>
       </c>
       <c r="I23" t="n">
-        <v>37.3</v>
+        <v>37.2</v>
       </c>
       <c r="J23" t="n">
         <v>81.59999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>0.457</v>
+        <v>0.456</v>
       </c>
       <c r="L23" t="n">
         <v>6.9</v>
       </c>
       <c r="M23" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="N23" t="n">
         <v>0.358</v>
@@ -4525,28 +4592,28 @@
         <v>0.735</v>
       </c>
       <c r="R23" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="S23" t="n">
-        <v>31.7</v>
+        <v>31.8</v>
       </c>
       <c r="T23" t="n">
-        <v>40.5</v>
+        <v>40.8</v>
       </c>
       <c r="U23" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="V23" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="W23" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="X23" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Y23" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="Z23" t="n">
         <v>21.2</v>
@@ -4555,10 +4622,10 @@
         <v>18.3</v>
       </c>
       <c r="AB23" t="n">
-        <v>95.90000000000001</v>
+        <v>95.7</v>
       </c>
       <c r="AC23" t="n">
-        <v>-5.8</v>
+        <v>-6</v>
       </c>
       <c r="AD23" t="n">
         <v>1</v>
@@ -4576,22 +4643,22 @@
         <v>26</v>
       </c>
       <c r="AI23" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AJ23" t="n">
         <v>23</v>
       </c>
       <c r="AK23" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AL23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AM23" t="n">
         <v>23</v>
       </c>
       <c r="AN23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AO23" t="n">
         <v>29</v>
@@ -4600,13 +4667,13 @@
         <v>29</v>
       </c>
       <c r="AQ23" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AR23" t="n">
         <v>28</v>
       </c>
       <c r="AS23" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AT23" t="n">
         <v>28</v>
@@ -4615,7 +4682,7 @@
         <v>24</v>
       </c>
       <c r="AV23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AW23" t="n">
         <v>15</v>
@@ -4624,16 +4691,16 @@
         <v>30</v>
       </c>
       <c r="AY23" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AZ23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA23" t="n">
         <v>29</v>
       </c>
       <c r="BB23" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BC23" t="n">
         <v>26</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>2-17-2014-15</t>
+          <t>2015-02-17</t>
         </is>
       </c>
     </row>
@@ -4755,7 +4822,7 @@
         <v>28</v>
       </c>
       <c r="AH24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI24" t="n">
         <v>30</v>
@@ -4806,13 +4873,13 @@
         <v>4</v>
       </c>
       <c r="AY24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA24" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BB24" t="n">
         <v>30</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>2-17-2014-15</t>
+          <t>2015-02-17</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>1.2</v>
       </c>
       <c r="AD25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE25" t="n">
         <v>14</v>
@@ -4973,10 +5040,10 @@
         <v>18</v>
       </c>
       <c r="AT25" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AU25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AV25" t="n">
         <v>22</v>
@@ -4994,7 +5061,7 @@
         <v>26</v>
       </c>
       <c r="BA25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BB25" t="n">
         <v>4</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>2-17-2014-15</t>
+          <t>2015-02-17</t>
         </is>
       </c>
     </row>
@@ -5125,7 +5192,7 @@
         <v>9</v>
       </c>
       <c r="AJ26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AK26" t="n">
         <v>19</v>
@@ -5137,7 +5204,7 @@
         <v>2</v>
       </c>
       <c r="AN26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO26" t="n">
         <v>27</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>2-17-2014-15</t>
+          <t>2015-02-17</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-4.2</v>
       </c>
       <c r="AD27" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AE27" t="n">
         <v>25</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>2-17-2014-15</t>
+          <t>2015-02-17</t>
         </is>
       </c>
     </row>
@@ -5393,67 +5460,67 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E28" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F28" t="n">
         <v>19</v>
       </c>
       <c r="G28" t="n">
-        <v>0.635</v>
+        <v>0.642</v>
       </c>
       <c r="H28" t="n">
-        <v>48.9</v>
+        <v>48.8</v>
       </c>
       <c r="I28" t="n">
         <v>37.9</v>
       </c>
       <c r="J28" t="n">
-        <v>83.59999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="K28" t="n">
-        <v>0.453</v>
+        <v>0.454</v>
       </c>
       <c r="L28" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="M28" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="N28" t="n">
-        <v>0.361</v>
+        <v>0.364</v>
       </c>
       <c r="O28" t="n">
-        <v>16.6</v>
+        <v>16.5</v>
       </c>
       <c r="P28" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.767</v>
+        <v>0.768</v>
       </c>
       <c r="R28" t="n">
-        <v>10.2</v>
+        <v>10.1</v>
       </c>
       <c r="S28" t="n">
-        <v>33.8</v>
+        <v>33.7</v>
       </c>
       <c r="T28" t="n">
-        <v>43.9</v>
+        <v>43.8</v>
       </c>
       <c r="U28" t="n">
         <v>24.3</v>
       </c>
       <c r="V28" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="W28" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="X28" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Y28" t="n">
         <v>4.8</v>
@@ -5468,16 +5535,16 @@
         <v>100.7</v>
       </c>
       <c r="AC28" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AD28" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="AE28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG28" t="n">
         <v>9</v>
@@ -5489,10 +5556,10 @@
         <v>13</v>
       </c>
       <c r="AJ28" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK28" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AL28" t="n">
         <v>11</v>
@@ -5501,25 +5568,25 @@
         <v>14</v>
       </c>
       <c r="AN28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO28" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AP28" t="n">
         <v>22</v>
       </c>
       <c r="AQ28" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AR28" t="n">
         <v>23</v>
       </c>
       <c r="AS28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT28" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AU28" t="n">
         <v>6</v>
@@ -5528,13 +5595,13 @@
         <v>14</v>
       </c>
       <c r="AW28" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AX28" t="n">
         <v>8</v>
       </c>
       <c r="AY28" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ28" t="n">
         <v>9</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>2-17-2014-15</t>
+          <t>2015-02-17</t>
         </is>
       </c>
     </row>
@@ -5671,10 +5738,10 @@
         <v>7</v>
       </c>
       <c r="AJ29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AK29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL29" t="n">
         <v>9</v>
@@ -5683,7 +5750,7 @@
         <v>8</v>
       </c>
       <c r="AN29" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO29" t="n">
         <v>3</v>
@@ -5713,7 +5780,7 @@
         <v>16</v>
       </c>
       <c r="AX29" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AY29" t="n">
         <v>19</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>2-17-2014-15</t>
+          <t>2015-02-17</t>
         </is>
       </c>
     </row>
@@ -5874,7 +5941,7 @@
         <v>16</v>
       </c>
       <c r="AQ30" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AR30" t="n">
         <v>9</v>
@@ -5895,7 +5962,7 @@
         <v>23</v>
       </c>
       <c r="AX30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY30" t="n">
         <v>17</v>
@@ -5907,7 +5974,7 @@
         <v>25</v>
       </c>
       <c r="BB30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BC30" t="n">
         <v>20</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>2-17-2014-15</t>
+          <t>2015-02-17</t>
         </is>
       </c>
     </row>
@@ -6017,10 +6084,10 @@
         <v>2.4</v>
       </c>
       <c r="AD31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AF31" t="n">
         <v>11</v>
@@ -6071,7 +6138,7 @@
         <v>5</v>
       </c>
       <c r="AV31" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AW31" t="n">
         <v>17</v>
@@ -6083,7 +6150,7 @@
         <v>8</v>
       </c>
       <c r="AZ31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA31" t="n">
         <v>17</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>2-17-2014-15</t>
+          <t>2015-02-17</t>
         </is>
       </c>
     </row>
